--- a/智能模型2026H2-OKR.xlsx
+++ b/智能模型2026H2-OKR.xlsx
@@ -834,8 +834,7 @@
 3. 持续迭代新老客风险模型，增强头部及尾部风险区分度。
 预期结果与衡量标准：
 - Non SACC 占比较基线相对提升【】%。
-- 风险表现维稳【】%。
-- 件均较基线相对提升【】%。</t>
+- 风险表现维稳【】%。</t>
         </is>
       </c>
       <c r="E4" s="1" t="n"/>

--- a/智能模型2026H2-OKR.xlsx
+++ b/智能模型2026H2-OKR.xlsx
@@ -786,15 +786,15 @@
       </c>
       <c r="C3" s="26" t="inlineStr">
         <is>
-          <t>KR1：2026 H2 累计放款规模达到【】million</t>
+          <t>KR1：2026 H2 累计放款规模达到117.2million</t>
         </is>
       </c>
       <c r="D3" s="27" t="inlineStr">
         <is>
           <t>预期结果与衡量标准：
-- H2 累计放款规模达到【】million。
-- 按月跟踪计划达成情况，确保半年度目标按期完成。
-- 风险指标：持续监控，确保风险表现稳定。</t>
+- H2 累计放款规模达到117.2M。
+- 风险表现维稳7.1%。
+- 按月跟踪计划达成情况，确保半年度目标按期完成。</t>
         </is>
       </c>
       <c r="E3" s="1" t="n"/>
@@ -833,8 +833,8 @@
 2. 构建投放质量追踪与归因分析基础设施，支撑投放效果评估与策略迭代。
 3. 持续迭代新老客风险模型，增强头部及尾部风险区分度。
 预期结果与衡量标准：
-- Non SACC 占比较基线相对提升【】%。
-- 风险表现维稳【】%。</t>
+- Non SACC 占比较基线相对提升5%。
+- 风险表现维稳7.1%。</t>
         </is>
       </c>
       <c r="E4" s="1" t="n"/>
@@ -866,7 +866,7 @@
 3. 共建净收益和 ROI 指标评价体系，支撑策略迭代与资源配置。
 预期结果与衡量标准：
 - 形成可核验的净收益评估结果，风险、成本和投诉等指标保持在业务阈值内。
-- 目标用户复购放款规模较基线相对提升【】%。</t>
+- T+7结清复购申请率目标准备60%。</t>
         </is>
       </c>
       <c r="E5" s="1" t="n"/>
@@ -900,7 +900,7 @@
 预期结果与衡量标准：
 - 分类识别覆盖率 ≥【】%，分类识别一致率 ≥【】%。
 - 核心结果可完整追溯、业务效果可量化评估。
-- 至少落地【】个风险场景和【】个用户画像或运营场景。</t>
+- 至少落地1个风险场景和1个用户画像或运营场景。</t>
         </is>
       </c>
       <c r="E6" s="1" t="n"/>
@@ -939,7 +939,7 @@
 2. 建设统一的商户、交易及标签知识库，完善更新、纠错和质量监控机制。
 3. 建立“发现问题—修复—验证—发布”的迭代闭环，持续治理高频错误和异常分类。
 预期结果与衡量标准：
-- 每月至少完成【1】次模型及知识库效果监控复盘。</t>
+- 每月至少完成1次模型及知识库效果监控复盘。</t>
         </is>
       </c>
       <c r="E7" s="1" t="n"/>
@@ -1041,10 +1041,7 @@
         <is>
           <t>重点专项：
 1. 以模型团队为核心枢纽，建立与市场、运营、投放团队的常态化联动机制；明确重点项目 Owner、里程碑和上下游依赖，持续跟踪进度与风险。
-2. 建立“需求对齐—联合开发—上线验证—效果复盘”的跨团队全流程协作闭环，推动模型能力在经营与风险决策中持续落地与迭代。
-预期结果与衡量标准：
-- 与市场、运营、投放团队的联动机制覆盖重点项目【】%；重点项目【】% 明确 Owner、里程碑和协作边界，并按计划完成关键交付。
-- 已上线重点项目【】% 完成跨团队效果复盘，输出可量化、可验证的价值结论，并沉淀可复用的协作模式。</t>
+2. 建立“需求对齐—联合开发—上线验证—效果复盘”的跨团队全流程协作闭环，推动模型能力在经营与风险决策中持续落地与迭代。</t>
         </is>
       </c>
       <c r="E10" s="1" t="n"/>

--- a/智能模型2026H2-OKR.xlsx
+++ b/智能模型2026H2-OKR.xlsx
@@ -833,8 +833,7 @@
 2. 构建投放质量追踪与归因分析基础设施，支撑投放效果评估与策略迭代。
 3. 持续迭代新老客风险模型，增强头部及尾部风险区分度。
 预期结果与衡量标准：
-- Non SACC 占比较基线相对提升5%。
-- 风险表现维稳7.1%。</t>
+- Non SACC 占比较基线相对提升5%。</t>
         </is>
       </c>
       <c r="E4" s="1" t="n"/>
@@ -898,7 +897,7 @@
 3. 建立模型结果追溯及业务效果评估机制。
 4. 建立模型及知识库运维体系。
 预期结果与衡量标准：
-- 分类识别覆盖率 ≥【】%，分类识别一致率 ≥【】%。
+- 分类识别覆盖率 ≥ 80%
 - 核心结果可完整追溯、业务效果可量化评估。
 - 至少落地1个风险场景和1个用户画像或运营场景。</t>
         </is>
@@ -1013,7 +1012,7 @@
       <c r="D9" s="27" t="inlineStr">
         <is>
           <t>预期结果与衡量标准：
-- 校招 HC 按计划【100】% 到岗。</t>
+- 校招 HC 按计划到岗。</t>
         </is>
       </c>
       <c r="E9" s="1" t="n"/>
